--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.34.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.34.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.34" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.34" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.34.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.34.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0034.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0034.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -855,7 +855,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.34.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.34.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.34" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.34" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: service of a Subp Ã¦ na on the Agent or Solicitor of the</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Vibait, 1 Phillips, 521 ； Cooper vs. Wood, 5 Beaven,</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜s office</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM].27</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM].27</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: symbol-only separator/garbage line :: . 27</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM].27</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,24 +676,24 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: subject:â€” Smith vs. H. M. Co., 1 Schoales &amp; Lefroy,</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: 391; Woodall vs. Walker, 3 Hare, 339 ； Hornby vs.</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: aintiffâ€™s.</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: æ°”</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 7</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -731,20 +735,16 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ ena to</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: /</t>
+          <t>L98: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -766,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -784,20 +784,16 @@
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: it, that the Subp Ã¦ na to answer be served on the Solicitor</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜subject â€”Smith vs. H. M. Co., 1 Schoales &amp; Lefroy,</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L100: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -831,11 +827,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Subp Ã¦ ena to</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -874,11 +866,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: That part of the above Order relating to Subp Ã¦ nas to</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -981,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1025,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1064,7 +1052,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
